--- a/curadoria/biblioteca_curadoria.xlsx
+++ b/curadoria/biblioteca_curadoria.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="80">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -117,6 +117,15 @@
     <t xml:space="preserve">Peso 0.908 kg/m (Alcoa) confirmado. Equivalencia visual confirmada. Contorno preciso pendente.</t>
   </si>
   <si>
+    <t xml:space="preserve">GEO-SU-024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marco Superior / Correr / Veneziana camarão para maxim-ar — família Suprema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delta peso ~3.2% conforme peso lido por Bruno no catálogo impresso da Vitral Sul — o OCR havia lido 0.959 (erro conhecido de OCR; Alcoa índice: 1.024). Equivalência visual confirmada. Contorno preciso pendente.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Perfil</t>
   </si>
   <si>
@@ -207,6 +216,18 @@
     <t xml:space="preserve">VitralSul: catálogo pág 74, PDF físico pág 74. Família local: Nobile 2.5.</t>
   </si>
   <si>
+    <t xml:space="preserve">ALCOA-SU-024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alcoa: catálogo pág ~160, PDF físico pág ~173.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-SU-024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VitralSul: catálogo pág ~75. Família local: Nobile 2.5.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Código</t>
   </si>
   <si>
@@ -225,13 +246,10 @@
     <t xml:space="preserve">Proveniência dos pesos</t>
   </si>
   <si>
-    <t xml:space="preserve">SU-024</t>
+    <t xml:space="preserve">SU-025</t>
   </si>
   <si>
     <t xml:space="preserve">Alcoa: índice do catálogo (texto nativo). Vitral Sul: OCR das páginas raster (confiança menor). Medição: 2026-07-09.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SU-025</t>
   </si>
   <si>
     <t xml:space="preserve">SU-056</t>
@@ -663,7 +681,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -854,6 +872,37 @@
         <v>30</v>
       </c>
     </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -870,7 +919,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -885,36 +934,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>13</v>
@@ -923,24 +972,24 @@
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>13</v>
@@ -949,24 +998,24 @@
         <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>21</v>
@@ -975,24 +1024,24 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -1001,24 +1050,24 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>24</v>
@@ -1027,24 +1076,24 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>24</v>
@@ -1053,24 +1102,24 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>27</v>
@@ -1079,24 +1128,24 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>27</v>
@@ -1105,16 +1154,68 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>60</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1133,7 +1234,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -1146,123 +1247,101 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1.024</v>
+        <v>0.973</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.959</v>
+        <v>0.919</v>
       </c>
       <c r="D2" s="4" t="n">
         <f aca="false">ABS(B2-C2)/MAX(B2,C2)</f>
-        <v>0.0634765625000001</v>
+        <v>0.0554984583761562</v>
       </c>
       <c r="E2" s="2" t="str">
-        <f aca="false">IF(D2&lt;$B$8,"✓ bate","⚠ olhar desenho")</f>
-        <v>⚠ olhar desenho</v>
+        <f aca="false">IF(D2&lt;$B$7,"✓ bate","⚠ olhar desenho")</f>
+        <v>✓ bate</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.973</v>
+        <v>0.539</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.919</v>
+        <v>0.519</v>
       </c>
       <c r="D3" s="4" t="n">
         <f aca="false">ABS(B3-C3)/MAX(B3,C3)</f>
-        <v>0.0554984583761562</v>
+        <v>0.0371057513914657</v>
       </c>
       <c r="E3" s="2" t="str">
-        <f aca="false">IF(D3&lt;$B$8,"✓ bate","⚠ olhar desenho")</f>
+        <f aca="false">IF(D3&lt;$B$7,"✓ bate","⚠ olhar desenho")</f>
         <v>✓ bate</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.539</v>
+        <v>1.006</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.519</v>
+        <v>0.969</v>
       </c>
       <c r="D4" s="4" t="n">
         <f aca="false">ABS(B4-C4)/MAX(B4,C4)</f>
-        <v>0.0371057513914657</v>
+        <v>0.036779324055666</v>
       </c>
       <c r="E4" s="2" t="str">
-        <f aca="false">IF(D4&lt;$B$8,"✓ bate","⚠ olhar desenho")</f>
+        <f aca="false">IF(D4&lt;$B$7,"✓ bate","⚠ olhar desenho")</f>
         <v>✓ bate</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>1.006</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0.969</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <f aca="false">ABS(B5-C5)/MAX(B5,C5)</f>
-        <v>0.036779324055666</v>
-      </c>
-      <c r="E5" s="2" t="str">
-        <f aca="false">IF(D5&lt;$B$8,"✓ bate","⚠ olhar desenho")</f>
-        <v>✓ bate</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="7" t="n">
         <v>0.06</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
-        <v>73</v>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/curadoria/biblioteca_curadoria.xlsx
+++ b/curadoria/biblioteca_curadoria.xlsx
@@ -120,10 +120,10 @@
     <t xml:space="preserve">GEO-SU-024</t>
   </si>
   <si>
-    <t xml:space="preserve">Marco Superior / Correr / Veneziana camarão para maxim-ar — família Suprema</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delta peso ~3.2% conforme peso lido por Bruno no catálogo impresso da Vitral Sul — o OCR havia lido 0.959 (erro conhecido de OCR; Alcoa índice: 1.024). Equivalência visual confirmada. Contorno preciso pendente.</t>
+    <t xml:space="preserve">Marco Superior / Correr / Veneziana camarão — família Suprema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delta peso ~3.2% conforme peso lido por Bruno no catálogo impresso da Vitral Sul — o OCR havia lido 0.959 (erro conhecido de OCR; Alcoa índice: 1.024). Equivalência visual confirmada. Contorno preciso pendente. CORRECAO: descricao anterior incluia 'maxim-ar' por engano do operador — removido.</t>
   </si>
   <si>
     <t xml:space="preserve">Perfil</t>

--- a/curadoria/biblioteca_curadoria.xlsx
+++ b/curadoria/biblioteca_curadoria.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="86">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -126,6 +126,15 @@
     <t xml:space="preserve">Delta peso ~3.2% conforme peso lido por Bruno no catálogo impresso da Vitral Sul — o OCR havia lido 0.959 (erro conhecido de OCR; Alcoa índice: 1.024). Equivalência visual confirmada. Contorno preciso pendente. CORRECAO: descricao anterior incluia 'maxim-ar' por engano do operador — removido.</t>
   </si>
   <si>
+    <t xml:space="preserve">GEO-SU-025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marco Inferior / Correr / Veneziana camarão — família Suprema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Par do SU-024 (marco superior). Equivalência visual confirmada. Contorno preciso pendente.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Perfil</t>
   </si>
   <si>
@@ -228,6 +237,18 @@
     <t xml:space="preserve">VitralSul: catálogo pág ~75. Família local: Nobile 2.5.</t>
   </si>
   <si>
+    <t xml:space="preserve">ALCOA-SU-025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alcoa: catálogo ~pág 160, PDF físico ~pág 173.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-SU-025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VitralSul: catálogo ~pág 75. Família local: Nobile 2.5.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Código</t>
   </si>
   <si>
@@ -246,13 +267,10 @@
     <t xml:space="preserve">Proveniência dos pesos</t>
   </si>
   <si>
-    <t xml:space="preserve">SU-025</t>
+    <t xml:space="preserve">SU-056</t>
   </si>
   <si>
     <t xml:space="preserve">Alcoa: índice do catálogo (texto nativo). Vitral Sul: OCR das páginas raster (confiança menor). Medição: 2026-07-09.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SU-056</t>
   </si>
   <si>
     <t xml:space="preserve">SU-280</t>
@@ -681,7 +699,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -903,6 +921,37 @@
         <v>33</v>
       </c>
     </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -919,7 +968,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -934,36 +983,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>13</v>
@@ -972,24 +1021,24 @@
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>13</v>
@@ -998,24 +1047,24 @@
         <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>21</v>
@@ -1024,24 +1073,24 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -1050,24 +1099,24 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>24</v>
@@ -1076,24 +1125,24 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>24</v>
@@ -1102,24 +1151,24 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>27</v>
@@ -1128,24 +1177,24 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>27</v>
@@ -1154,24 +1203,24 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>31</v>
@@ -1180,24 +1229,24 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>31</v>
@@ -1206,16 +1255,68 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1234,7 +1335,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -1247,101 +1348,79 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.973</v>
+        <v>0.539</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.919</v>
+        <v>0.519</v>
       </c>
       <c r="D2" s="4" t="n">
         <f aca="false">ABS(B2-C2)/MAX(B2,C2)</f>
-        <v>0.0554984583761562</v>
+        <v>0.0371057513914657</v>
       </c>
       <c r="E2" s="2" t="str">
-        <f aca="false">IF(D2&lt;$B$7,"✓ bate","⚠ olhar desenho")</f>
+        <f aca="false">IF(D2&lt;$B$6,"✓ bate","⚠ olhar desenho")</f>
         <v>✓ bate</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.539</v>
+        <v>1.006</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.519</v>
+        <v>0.969</v>
       </c>
       <c r="D3" s="4" t="n">
         <f aca="false">ABS(B3-C3)/MAX(B3,C3)</f>
-        <v>0.0371057513914657</v>
+        <v>0.036779324055666</v>
       </c>
       <c r="E3" s="2" t="str">
-        <f aca="false">IF(D3&lt;$B$7,"✓ bate","⚠ olhar desenho")</f>
+        <f aca="false">IF(D3&lt;$B$6,"✓ bate","⚠ olhar desenho")</f>
         <v>✓ bate</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>1.006</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>0.969</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <f aca="false">ABS(B4-C4)/MAX(B4,C4)</f>
-        <v>0.036779324055666</v>
-      </c>
-      <c r="E4" s="2" t="str">
-        <f aca="false">IF(D4&lt;$B$7,"✓ bate","⚠ olhar desenho")</f>
-        <v>✓ bate</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="7" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="7" t="n">
         <v>0.06</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>79</v>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/curadoria/biblioteca_curadoria.xlsx
+++ b/curadoria/biblioteca_curadoria.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -135,6 +135,15 @@
     <t xml:space="preserve">Par do SU-024 (marco superior). Equivalência visual confirmada. Contorno preciso pendente.</t>
   </si>
   <si>
+    <t xml:space="preserve">GEO-SU-056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montante mão de amigo — família Suprema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equivalência visual confirmada. Contorno preciso pendente.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Perfil</t>
   </si>
   <si>
@@ -249,6 +258,18 @@
     <t xml:space="preserve">VitralSul: catálogo ~pág 75. Família local: Nobile 2.5.</t>
   </si>
   <si>
+    <t xml:space="preserve">ALCOA-SU-056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alcoa: catálogo ~pág 163, PDF físico ~pág 176.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-SU-056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VitralSul: catálogo ~pág 78. Família local: Nobile 2.5.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Código</t>
   </si>
   <si>
@@ -267,13 +288,10 @@
     <t xml:space="preserve">Proveniência dos pesos</t>
   </si>
   <si>
-    <t xml:space="preserve">SU-056</t>
+    <t xml:space="preserve">SU-280</t>
   </si>
   <si>
     <t xml:space="preserve">Alcoa: índice do catálogo (texto nativo). Vitral Sul: OCR das páginas raster (confiança menor). Medição: 2026-07-09.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SU-280</t>
   </si>
   <si>
     <t xml:space="preserve">Tolerância Δ peso:</t>
@@ -699,7 +717,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -952,6 +970,37 @@
         <v>36</v>
       </c>
     </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -968,7 +1017,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -983,36 +1032,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>13</v>
@@ -1021,24 +1070,24 @@
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>13</v>
@@ -1047,24 +1096,24 @@
         <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>21</v>
@@ -1073,24 +1122,24 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -1099,24 +1148,24 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>24</v>
@@ -1125,24 +1174,24 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>24</v>
@@ -1151,24 +1200,24 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>27</v>
@@ -1177,24 +1226,24 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>27</v>
@@ -1203,24 +1252,24 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>31</v>
@@ -1229,24 +1278,24 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>31</v>
@@ -1255,24 +1304,24 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>34</v>
@@ -1281,24 +1330,24 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>34</v>
@@ -1307,16 +1356,68 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1335,7 +1436,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -1348,79 +1449,57 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.539</v>
+        <v>1.006</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.519</v>
+        <v>0.969</v>
       </c>
       <c r="D2" s="4" t="n">
         <f aca="false">ABS(B2-C2)/MAX(B2,C2)</f>
-        <v>0.0371057513914657</v>
+        <v>0.036779324055666</v>
       </c>
       <c r="E2" s="2" t="str">
-        <f aca="false">IF(D2&lt;$B$6,"✓ bate","⚠ olhar desenho")</f>
+        <f aca="false">IF(D2&lt;$B$5,"✓ bate","⚠ olhar desenho")</f>
         <v>✓ bate</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>1.006</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0.969</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <f aca="false">ABS(B3-C3)/MAX(B3,C3)</f>
-        <v>0.036779324055666</v>
-      </c>
-      <c r="E3" s="2" t="str">
-        <f aca="false">IF(D3&lt;$B$6,"✓ bate","⚠ olhar desenho")</f>
-        <v>✓ bate</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="B6" s="7" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="7" t="n">
         <v>0.06</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
-        <v>85</v>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/curadoria/biblioteca_curadoria.xlsx
+++ b/curadoria/biblioteca_curadoria.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="96">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -144,6 +144,12 @@
     <t xml:space="preserve">Equivalência visual confirmada. Contorno preciso pendente.</t>
   </si>
   <si>
+    <t xml:space="preserve">GEO-SU-280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montante lateral/folha — família Suprema</t>
+  </si>
+  <si>
     <t xml:space="preserve">Perfil</t>
   </si>
   <si>
@@ -270,6 +276,18 @@
     <t xml:space="preserve">VitralSul: catálogo ~pág 78. Família local: Nobile 2.5.</t>
   </si>
   <si>
+    <t xml:space="preserve">ALCOA-SU-280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alcoa: catálogo ~pág 165, PDF físico ~pág 178.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-SU-280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VitralSul: catálogo ~pág 80. Família local: Nobile 2.5.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Código</t>
   </si>
   <si>
@@ -286,12 +304,6 @@
   </si>
   <si>
     <t xml:space="preserve">Proveniência dos pesos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SU-280</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alcoa: índice do catálogo (texto nativo). Vitral Sul: OCR das páginas raster (confiança menor). Medição: 2026-07-09.</t>
   </si>
   <si>
     <t xml:space="preserve">Tolerância Δ peso:</t>
@@ -308,7 +320,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -346,22 +358,15 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -428,7 +433,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -445,23 +450,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -717,7 +710,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -1001,6 +994,37 @@
         <v>39</v>
       </c>
     </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1017,7 +1041,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -1032,36 +1056,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>13</v>
@@ -1070,24 +1094,24 @@
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>13</v>
@@ -1096,24 +1120,24 @@
         <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>21</v>
@@ -1122,24 +1146,24 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -1148,24 +1172,24 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>24</v>
@@ -1174,24 +1198,24 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>24</v>
@@ -1200,24 +1224,24 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>27</v>
@@ -1226,24 +1250,24 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>27</v>
@@ -1252,24 +1276,24 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>31</v>
@@ -1278,24 +1302,24 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>31</v>
@@ -1304,24 +1328,24 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>34</v>
@@ -1330,24 +1354,24 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>34</v>
@@ -1356,24 +1380,24 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>37</v>
@@ -1382,24 +1406,24 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>37</v>
@@ -1408,16 +1432,68 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>81</v>
+      <c r="C16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1436,7 +1512,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -1449,57 +1525,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>1.006</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>0.969</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <f aca="false">ABS(B2-C2)/MAX(B2,C2)</f>
-        <v>0.036779324055666</v>
-      </c>
-      <c r="E2" s="2" t="str">
-        <f aca="false">IF(D2&lt;$B$5,"✓ bate","⚠ olhar desenho")</f>
-        <v>✓ bate</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B5" s="7" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="4" t="n">
         <v>0.06</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>91</v>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/curadoria/biblioteca_curadoria.xlsx
+++ b/curadoria/biblioteca_curadoria.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="135">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -150,6 +150,9 @@
     <t xml:space="preserve">Montante lateral/folha — família Suprema</t>
   </si>
   <si>
+    <t xml:space="preserve">Equivalência visual confirmada. Contorno preciso pendente. ASA (MG25) não possui equivalente catalogado para este perfil.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Perfil</t>
   </si>
   <si>
@@ -286,6 +289,120 @@
   </si>
   <si>
     <t xml:space="preserve">VitralSul: catálogo ~pág 80. Família local: Nobile 2.5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMS-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamboré</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comparação visual no catálogo impresso — 5 fabricantes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamboré TMS-005. Mesma geometria Alcoa/VitralSul já homologada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMS-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centenário</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centenário TMS-005. Peso difere ligeiramente do Tamboré apesar da mesma nomenclatura — observação de mercado registrada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG25-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA MG25-005. Mesma geometria confirmada por Bruno.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMS-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamboré TMS-009.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMS-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centenário TMS-009. Peso difere ligeiramente do Tamboré.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG25-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA MG25-009.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMS-056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamboré TMS-056.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMS-056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centenário TMS-056. Peso difere ligeiramente do Tamboré.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG25-056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA MG25-056.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMS-228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamboré TMS-228.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMS-228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centenário TMS-228. Peso difere ligeiramente do Tamboré.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG25-228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA MG25-228. Altura 1mm maior que SU-228 — não altera usabilidade. Decisão Bruno: mesma GeometriaPadrao.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMS-230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamboré TMS-230.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMS-230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centenário TMS-230. Peso difere ligeiramente do Tamboré.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG25-230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA MG25-230. Altura 1mm maior que SU-230 — não altera usabilidade. Decisão Bruno: mesma GeometriaPadrao.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMS-280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamboré TMS-280.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMS-280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centenário TMS-280. Peso difere ligeiramente do Tamboré.</t>
   </si>
   <si>
     <t xml:space="preserve">Código</t>
@@ -1022,7 +1139,7 @@
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1041,7 +1158,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -1056,36 +1173,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>13</v>
@@ -1094,24 +1211,24 @@
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>13</v>
@@ -1120,24 +1237,24 @@
         <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>21</v>
@@ -1146,24 +1263,24 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -1172,24 +1289,24 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>24</v>
@@ -1198,24 +1315,24 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>24</v>
@@ -1224,24 +1341,24 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>27</v>
@@ -1250,24 +1367,24 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>27</v>
@@ -1276,24 +1393,24 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>31</v>
@@ -1302,24 +1419,24 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>31</v>
@@ -1328,24 +1445,24 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>34</v>
@@ -1354,24 +1471,24 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>34</v>
@@ -1380,24 +1497,24 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>37</v>
@@ -1406,24 +1523,24 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>37</v>
@@ -1432,24 +1549,24 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>40</v>
@@ -1458,24 +1575,24 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>40</v>
@@ -1484,16 +1601,458 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -1525,27 +2084,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>0.06</v>
@@ -1553,7 +2112,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/curadoria/biblioteca_curadoria.xlsx
+++ b/curadoria/biblioteca_curadoria.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2357" uniqueCount="554">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -153,6 +153,291 @@
     <t xml:space="preserve">Equivalência visual confirmada. Contorno preciso pendente. ASA (MG25) não possui equivalente catalogado para este perfil.</t>
   </si>
   <si>
+    <t xml:space="preserve">GEO-LG-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marco Lateral Vertical — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOLD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. Aliases: ASA: MG32-016.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marco Bandeira / Peitoril — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. Aliases: ASA: MG32-017.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travessa Intermediária - Bandeira — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. Aliases: ASA: MG32-018.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folha Inferior e Superior Horizontal — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. Aliases: ASA: MG32-020.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folha Inferior Horizontal — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. Aliases: ASA: MG32-032.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trilho superior — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. NOTA: presente só nos catálogos Alcoa/Hydro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marco — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trilho superior 3 planos — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baguete — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. Aliases: ASA: MG32-115.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arremate Porta de Giro — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. Aliases: ASA: MG32-029.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folha Lateral Vertical com Reforço — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mão de amigo — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. Aliases: ASA: MG32-055.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folha — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. NOTA: peso G3 1.016 x G4 1.116 (9%), mas Bruno confirmou MESMA geometria.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travessa — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trilho 2 planos — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baguete Vertical — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. NOTA: MG32 3mm de diferença — não altera usabilidade. Aliases: ASA: MG32-057.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baguete Veneziana — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. Aliases: ASA: MG32-114.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complemento - Marco Lateral — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. Aliases: ASA: MG32-024.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. NOTA: sem equivalente em alguns catálogos; existe em Gold3 e Gold4 Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folha Perimetral Porta de Giro — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. Aliases: ASA: MG32-011.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marco Superior Horizontal — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. Aliases: Alcoa base: SI-301; ASA: MG32-001.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folha Mão de Amigo - Interno — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. Aliases: Alcoa base: SI-309; ASA: MG32-005.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folha Mão de Amigo - Externo — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. Aliases: Alcoa base: SI-310; ASA: MG32-006.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folha Lateral / Central Vertical — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. Aliases: Alcoa base: SI-311.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folha Central Vertical — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. Aliases: Alcoa base: SI-312.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. Aliases: ASA: MG32-054.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. NOTA: 1mm de diferença na medida — não altera usabilidade. Aliases: Alcoa base: SI-314; ASA: MG32-053.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. NOTA: 1mm de diferença na medida — não altera usabilidade. Aliases: Alcoa base: SI-315; ASA: MG32-056.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travessa Horizontal — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. Aliases: Alcoa base: SI-317; ASA: MG32-009.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marco Porta de Giro — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. Aliases: Alcoa base: SI-319; ASA: MG32-010.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. Aliases: Alcoa base: SI-324; ASA: MG32-026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baguete Horizontal — família Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. NOTA: MG32 2mm de diferença — não altera usabilidade. Aliases: Alcoa base: SI-328; ASA: MG32-012.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-LG-062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homologação em lote família Gold. Equivalência confirmada por curadoria visual do Bruno em todos os catálogos. Contorno preciso pendente. Aliases: Alcoa base: SI-343.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Perfil</t>
   </si>
   <si>
@@ -403,6 +688,978 @@
   </si>
   <si>
     <t xml:space="preserve">Centenário TMS-280. Peso difere ligeiramente do Tamboré.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comparação visual no catálogo impresso — família Gold, múltiplos fabricantes e gerações</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-002.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-002 (equivale a LG-002). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG32-016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura ASA MG32-016 (equivale a LG-002).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-003.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-003 (equivale a LG-003). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG32-017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura ASA MG32-017 (equivale a LG-003).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-004.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-004 (equivale a LG-004). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG32-018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura ASA MG32-018 (equivale a LG-004).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-006.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-006 (equivale a LG-006). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG32-020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura ASA MG32-020 (equivale a LG-006).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-007.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-007 (equivale a LG-007). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG32-032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura ASA MG32-032 (equivale a LG-007).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-008.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-008 (equivale a LG-008). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-009.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-009 (equivale a LG-009). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-010.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-010 (equivale a LG-010). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-011.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-011 (equivale a LG-011). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-014.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-014 (equivale a LG-014). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-015.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-015 (equivale a LG-015). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG32-115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura ASA MG32-115 (equivale a LG-015).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-016.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-016 (equivale a LG-016). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG32-029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura ASA MG32-029 (equivale a LG-016).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-017.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-017 (equivale a LG-017). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-018.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-018 (equivale a LG-018). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG32-055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura ASA MG32-055 (equivale a LG-018).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-019.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-019 (equivale a LG-019). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-020.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-020 (equivale a LG-020). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-021.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-021 (equivale a LG-021). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-022.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-022 (equivale a LG-022). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-023.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-023 (equivale a LG-023). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-025.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-025 (equivale a LG-025). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-026 (equivale a LG-026). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG32-057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura ASA MG32-057 (equivale a LG-026). MG32 3mm de diferença — não altera usabilidade.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-027.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-027 (equivale a LG-027). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG32-114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura ASA MG32-114 (equivale a LG-027).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-028.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-028 (equivale a LG-028). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG32-024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura ASA MG32-024 (equivale a LG-028).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-042.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-042 (equivale a LG-042). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-043.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-043 (equivale a LG-043). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG32-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura ASA MG32-011 (equivale a LG-043).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-044. Alias base Alcoa: SI-301.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-044.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-044 (equivale a LG-044). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG32-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura ASA MG32-001 (equivale a LG-044).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-048. Alias base Alcoa: SI-309.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-048.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-048 (equivale a LG-048). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG32-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura ASA MG32-005 (equivale a LG-048).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-049. Alias base Alcoa: SI-310.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-049.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-049 (equivale a LG-049). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG32-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura ASA MG32-006 (equivale a LG-049).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-050. Alias base Alcoa: SI-311.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-050.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-050 (equivale a LG-050). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-051. Alias base Alcoa: SI-312.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-051.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-051 (equivale a LG-051). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-052.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-052 (equivale a LG-052). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG32-054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura ASA MG32-054 (equivale a LG-052).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-053. Alias base Alcoa: SI-314.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-053.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-053 (equivale a LG-053). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG32-053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura ASA MG32-053 (equivale a LG-053).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-054. Alias base Alcoa: SI-315.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-054.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-054 (equivale a LG-054). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG32-056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura ASA MG32-056 (equivale a LG-054).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-055. Alias base Alcoa: SI-317.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-055.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-055 (equivale a LG-055). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG32-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura ASA MG32-009 (equivale a LG-055).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-056. Alias base Alcoa: SI-319.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-056.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-056 (equivale a LG-056). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG32-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura ASA MG32-010 (equivale a LG-056).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-058. Alias base Alcoa: SI-324.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-058.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-058 (equivale a LG-058). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG32-026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura ASA MG32-026 (equivale a LG-058).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-059. Alias base Alcoa: SI-328.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-059.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-059 (equivale a LG-059). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASA-MG32-012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura ASA MG32-012 (equivale a LG-059). MG32 2mm de diferença — não altera usabilidade.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOA-LG-062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-062. Alias base Alcoa: SI-343.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRO-LG-062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura LG-062.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITRALSUL-LG-062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTENARIO-TMG-062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Família Gold. Nomenclatura local TMG-062 (equivale a LG-062). Pesos diferem do padrão Alcoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBORE-TMG-062</t>
   </si>
   <si>
     <t xml:space="preserve">Código</t>
@@ -827,7 +2084,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -1142,6 +2399,1184 @@
         <v>42</v>
       </c>
     </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1158,7 +3593,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H246"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -1173,36 +3608,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>138</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>139</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>140</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>46</v>
+        <v>141</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>47</v>
+        <v>142</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>48</v>
+        <v>143</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>49</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>50</v>
+        <v>145</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>13</v>
@@ -1211,24 +3646,24 @@
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>52</v>
+        <v>147</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>13</v>
@@ -1237,24 +3672,24 @@
         <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>52</v>
+        <v>147</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>57</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>58</v>
+        <v>153</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>21</v>
@@ -1263,24 +3698,24 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>60</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>61</v>
+        <v>156</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -1289,24 +3724,24 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>62</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>63</v>
+        <v>158</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>24</v>
@@ -1315,24 +3750,24 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>64</v>
+        <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>65</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>24</v>
@@ -1341,24 +3776,24 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>64</v>
+        <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>67</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>27</v>
@@ -1367,24 +3802,24 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>71</v>
+        <v>166</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>27</v>
@@ -1393,24 +3828,24 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>72</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>31</v>
@@ -1419,24 +3854,24 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>74</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>31</v>
@@ -1445,24 +3880,24 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>76</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>77</v>
+        <v>172</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>34</v>
@@ -1471,24 +3906,24 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>78</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>79</v>
+        <v>174</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>34</v>
@@ -1497,24 +3932,24 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>80</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>81</v>
+        <v>176</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>37</v>
@@ -1523,24 +3958,24 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>82</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>83</v>
+        <v>178</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>37</v>
@@ -1549,24 +3984,24 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>84</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>40</v>
@@ -1575,24 +4010,24 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>86</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>87</v>
+        <v>182</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>40</v>
@@ -1601,24 +4036,24 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>88</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>13</v>
@@ -1627,24 +4062,24 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>91</v>
+        <v>186</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>92</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>93</v>
+        <v>188</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>94</v>
+        <v>189</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>13</v>
@@ -1653,24 +4088,24 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>91</v>
+        <v>186</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>95</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>96</v>
+        <v>191</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>97</v>
+        <v>192</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>13</v>
@@ -1679,24 +4114,24 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>91</v>
+        <v>186</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>98</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>99</v>
+        <v>194</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>27</v>
@@ -1705,24 +4140,24 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>91</v>
+        <v>186</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>100</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>101</v>
+        <v>196</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>94</v>
+        <v>189</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>27</v>
@@ -1731,24 +4166,24 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>91</v>
+        <v>186</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>102</v>
+        <v>197</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>97</v>
+        <v>192</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>27</v>
@@ -1757,24 +4192,24 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>91</v>
+        <v>186</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>104</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>105</v>
+        <v>200</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>37</v>
@@ -1783,24 +4218,24 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>91</v>
+        <v>186</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>106</v>
+        <v>201</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>107</v>
+        <v>202</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>94</v>
+        <v>189</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>37</v>
@@ -1809,24 +4244,24 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>91</v>
+        <v>186</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>108</v>
+        <v>203</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>109</v>
+        <v>204</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>97</v>
+        <v>192</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>37</v>
@@ -1835,24 +4270,24 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>91</v>
+        <v>186</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>110</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>111</v>
+        <v>206</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>21</v>
@@ -1861,24 +4296,24 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>91</v>
+        <v>186</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>112</v>
+        <v>207</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>113</v>
+        <v>208</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>94</v>
+        <v>189</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>21</v>
@@ -1887,24 +4322,24 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>91</v>
+        <v>186</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>114</v>
+        <v>209</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>115</v>
+        <v>210</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>97</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>21</v>
@@ -1913,24 +4348,24 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>91</v>
+        <v>186</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>116</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>117</v>
+        <v>212</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>24</v>
@@ -1939,24 +4374,24 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>91</v>
+        <v>186</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>118</v>
+        <v>213</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>119</v>
+        <v>214</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>94</v>
+        <v>189</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>24</v>
@@ -1965,24 +4400,24 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>91</v>
+        <v>186</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>120</v>
+        <v>215</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>121</v>
+        <v>216</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>97</v>
+        <v>192</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>24</v>
@@ -1991,24 +4426,24 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>91</v>
+        <v>186</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>122</v>
+        <v>217</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>123</v>
+        <v>218</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>40</v>
@@ -2017,24 +4452,24 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>91</v>
+        <v>186</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>124</v>
+        <v>219</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>125</v>
+        <v>220</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>94</v>
+        <v>189</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>40</v>
@@ -2043,16 +4478,5528 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>91</v>
+        <v>186</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G34" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H34" s="2" t="s">
-        <v>126</v>
+      <c r="D53" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H167" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H168" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H169" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H170" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H171" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H172" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H173" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H175" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H176" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F177" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H177" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H178" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H179" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H180" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H181" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H183" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F184" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H184" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H185" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H186" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H187" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H188" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H189" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H190" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G191" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H191" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F192" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G192" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H192" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H193" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F194" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H194" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H195" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F196" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G196" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H196" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H197" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G198" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H198" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G199" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H199" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H200" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H201" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G202" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H202" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G203" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H203" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G204" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H204" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H205" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H206" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F207" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G207" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H207" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G208" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H208" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G209" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H209" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G210" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H210" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F211" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G211" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H211" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G212" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H212" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G213" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H213" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F214" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G214" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H214" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F215" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G215" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H215" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F216" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G216" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H216" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F217" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G217" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H217" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F218" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G218" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H218" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F219" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G219" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H219" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F220" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G220" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H220" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F221" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G221" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H221" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F222" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G222" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H222" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F223" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G223" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H223" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F224" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G224" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H224" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F225" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G225" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H225" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G226" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H226" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F227" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G227" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H227" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F228" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G228" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H228" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F229" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G229" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H229" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F230" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G230" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H230" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F231" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G231" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H231" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G232" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H232" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F233" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G233" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H233" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F234" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G234" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H234" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F235" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G235" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H235" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F236" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G236" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H236" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F237" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G237" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H237" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F238" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G238" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H238" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F239" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G239" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H239" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A240" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F240" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G240" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H240" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F241" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G241" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H241" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F242" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G242" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H242" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F243" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G243" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H243" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F244" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G244" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H244" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F245" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G245" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H245" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F246" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G246" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H246" s="2" t="s">
+        <v>544</v>
       </c>
     </row>
   </sheetData>
@@ -2084,27 +10031,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>546</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>547</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>129</v>
+        <v>548</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>130</v>
+        <v>549</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>131</v>
+        <v>550</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>132</v>
+        <v>551</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>133</v>
+        <v>552</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>0.06</v>
@@ -2112,7 +10059,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>134</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
